--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/MINNESOTA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/MINNESOTA_2022.xlsx
@@ -1039,7 +1039,7 @@
         <v>5</v>
       </c>
       <c r="D38">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="39">
@@ -1561,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="68">
@@ -1615,7 +1615,7 @@
         <v>5</v>
       </c>
       <c r="D70">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="71">
@@ -2353,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="D111">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="112">
@@ -2479,7 +2479,7 @@
         <v>5</v>
       </c>
       <c r="D118">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="119">
@@ -2677,7 +2677,7 @@
         <v>5</v>
       </c>
       <c r="D129">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="130">
@@ -2821,7 +2821,7 @@
         <v>5</v>
       </c>
       <c r="D137">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="138">
@@ -3055,7 +3055,7 @@
         <v>5</v>
       </c>
       <c r="D150">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="151">
@@ -3433,7 +3433,7 @@
         <v>5</v>
       </c>
       <c r="D171">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="172">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C199">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C208">
@@ -4603,7 +4603,7 @@
         <v>5</v>
       </c>
       <c r="D236">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="237">
@@ -4711,7 +4711,7 @@
         <v>5</v>
       </c>
       <c r="D242">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="243">
@@ -4855,7 +4855,7 @@
         <v>5</v>
       </c>
       <c r="D250">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="251">
@@ -5107,7 +5107,7 @@
         <v>5</v>
       </c>
       <c r="D264">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="265">
@@ -5197,7 +5197,7 @@
         <v>5</v>
       </c>
       <c r="D269">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="270">
@@ -5665,7 +5665,7 @@
         <v>5</v>
       </c>
       <c r="D295">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="296">
@@ -5935,7 +5935,7 @@
         <v>5</v>
       </c>
       <c r="D310">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="311">
@@ -6313,7 +6313,7 @@
         <v>5</v>
       </c>
       <c r="D331">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="332">
@@ -6961,7 +6961,7 @@
         <v>5</v>
       </c>
       <c r="D367">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="368">
@@ -6979,7 +6979,7 @@
         <v>5</v>
       </c>
       <c r="D368">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="369">
@@ -6997,7 +6997,7 @@
         <v>5</v>
       </c>
       <c r="D369">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="370">
@@ -7843,7 +7843,7 @@
         <v>5</v>
       </c>
       <c r="D416">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="417">
@@ -8239,7 +8239,7 @@
         <v>5</v>
       </c>
       <c r="D438">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="439">
@@ -8275,7 +8275,7 @@
         <v>5</v>
       </c>
       <c r="D440">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="441">
@@ -8383,7 +8383,7 @@
         <v>5</v>
       </c>
       <c r="D446">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="447">
@@ -8635,7 +8635,7 @@
         <v>5</v>
       </c>
       <c r="D460">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="461">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C494">
@@ -9931,7 +9931,7 @@
         <v>5</v>
       </c>
       <c r="D532">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="533">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C552">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C573">
@@ -11083,7 +11083,7 @@
         <v>5</v>
       </c>
       <c r="D596">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="597">
@@ -11425,7 +11425,7 @@
         <v>5</v>
       </c>
       <c r="D615">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="616">
@@ -12001,7 +12001,7 @@
         <v>5</v>
       </c>
       <c r="D647">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="648">
@@ -12073,7 +12073,7 @@
         <v>5</v>
       </c>
       <c r="D651">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="652">
@@ -12667,7 +12667,7 @@
         <v>5</v>
       </c>
       <c r="D684">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="685">
@@ -12937,7 +12937,7 @@
         <v>5</v>
       </c>
       <c r="D699">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="700">
@@ -13693,7 +13693,7 @@
         <v>5</v>
       </c>
       <c r="D741">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="742">
@@ -13747,7 +13747,7 @@
         <v>5</v>
       </c>
       <c r="D744">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="745">
@@ -13981,7 +13981,7 @@
         <v>5</v>
       </c>
       <c r="D757">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="758">
@@ -14251,7 +14251,7 @@
         <v>5</v>
       </c>
       <c r="D772">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="773">
@@ -15313,7 +15313,7 @@
         <v>5</v>
       </c>
       <c r="D831">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="832">
@@ -15565,7 +15565,7 @@
         <v>5</v>
       </c>
       <c r="D845">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="846">
@@ -16195,7 +16195,7 @@
         <v>5</v>
       </c>
       <c r="D880">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="881">
@@ -16375,7 +16375,7 @@
         <v>5</v>
       </c>
       <c r="D890">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
     <row r="891">
@@ -17437,7 +17437,7 @@
         <v>5</v>
       </c>
       <c r="D949">
-        <v>0.0009218289085545723</v>
+        <v>0.0009218289085545724</v>
       </c>
     </row>
   </sheetData>
